--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122634371</v>
+        <v>122639147</v>
       </c>
       <c r="B2" t="n">
-        <v>91243</v>
+        <v>94651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468912</v>
+        <v>468885</v>
       </c>
       <c r="R2" t="n">
-        <v>6295351</v>
+        <v>6295295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,17 +788,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Darell, Caroline Mortlock</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122639147</v>
+        <v>122634371</v>
       </c>
       <c r="B3" t="n">
-        <v>94651</v>
+        <v>91243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,35 +811,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468885</v>
+        <v>468912</v>
       </c>
       <c r="R3" t="n">
-        <v>6295295</v>
+        <v>6295351</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,6 +882,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Per Darell, Caroline Mortlock</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122639147</v>
       </c>
       <c r="B2" t="n">
-        <v>94651</v>
+        <v>94652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>122634371</v>
       </c>
       <c r="B3" t="n">
-        <v>91243</v>
+        <v>91244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122639147</v>
       </c>
       <c r="B2" t="n">
-        <v>94652</v>
+        <v>94655</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>122634371</v>
       </c>
       <c r="B3" t="n">
-        <v>91244</v>
+        <v>91247</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122639147</v>
+        <v>122634371</v>
       </c>
       <c r="B2" t="n">
-        <v>94655</v>
+        <v>91247</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468885</v>
+        <v>468912</v>
       </c>
       <c r="R2" t="n">
-        <v>6295295</v>
+        <v>6295351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +762,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,17 +792,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Per Darell, Caroline Mortlock</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122634371</v>
+        <v>122639147</v>
       </c>
       <c r="B3" t="n">
-        <v>91247</v>
+        <v>94655</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,34 +815,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -846,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468912</v>
+        <v>468885</v>
       </c>
       <c r="R3" t="n">
-        <v>6295351</v>
+        <v>6295295</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,11 +887,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Darell, Caroline Mortlock</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,121 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122607861</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97303</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Avd 55, Mellansjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>468898</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6295261</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Blädinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Grova barrträd med torrakor och lågor, fuktig mark intill maden.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122639147</v>
+        <v>122634371</v>
       </c>
       <c r="B2" t="n">
-        <v>94758</v>
+        <v>91354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468885</v>
+        <v>468912</v>
       </c>
       <c r="R2" t="n">
-        <v>6295295</v>
+        <v>6295351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +762,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,17 +792,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Per Darell, Caroline Mortlock</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122634371</v>
+        <v>122639147</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>94766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,34 +815,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -846,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468912</v>
+        <v>468885</v>
       </c>
       <c r="R3" t="n">
-        <v>6295351</v>
+        <v>6295295</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,11 +887,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Darell, Caroline Mortlock</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>122607861</v>
       </c>
       <c r="B4" t="n">
-        <v>97303</v>
+        <v>97311</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122634371</v>
+        <v>122639147</v>
       </c>
       <c r="B2" t="n">
-        <v>91354</v>
+        <v>94766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468912</v>
+        <v>468885</v>
       </c>
       <c r="R2" t="n">
-        <v>6295351</v>
+        <v>6295295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,17 +788,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Darell, Caroline Mortlock</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122639147</v>
+        <v>122634371</v>
       </c>
       <c r="B3" t="n">
-        <v>94766</v>
+        <v>91354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,35 +811,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468885</v>
+        <v>468912</v>
       </c>
       <c r="R3" t="n">
-        <v>6295295</v>
+        <v>6295351</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,6 +882,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Per Darell, Caroline Mortlock</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122639147</v>
       </c>
       <c r="B2" t="n">
-        <v>94766</v>
+        <v>94768</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>122607861</v>
       </c>
       <c r="B4" t="n">
-        <v>97311</v>
+        <v>97313</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122639147</v>
+        <v>122634371</v>
       </c>
       <c r="B2" t="n">
-        <v>94768</v>
+        <v>91354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468885</v>
+        <v>468912</v>
       </c>
       <c r="R2" t="n">
-        <v>6295295</v>
+        <v>6295351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +762,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,17 +792,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Per Darell, Caroline Mortlock</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122634371</v>
+        <v>122639147</v>
       </c>
       <c r="B3" t="n">
-        <v>91354</v>
+        <v>94768</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,34 +815,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -846,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468912</v>
+        <v>468885</v>
       </c>
       <c r="R3" t="n">
-        <v>6295351</v>
+        <v>6295295</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,11 +887,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Darell, Caroline Mortlock</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122634371</v>
       </c>
       <c r="B2" t="n">
-        <v>91354</v>
+        <v>91362</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>122639147</v>
       </c>
       <c r="B3" t="n">
-        <v>94768</v>
+        <v>94776</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>122607861</v>
       </c>
       <c r="B4" t="n">
-        <v>97313</v>
+        <v>97321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,6 +1032,126 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123204693</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mellansjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>468906</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6295262</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Blädinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>122607861</v>
       </c>
       <c r="B4" t="n">
-        <v>97321</v>
+        <v>97324</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>123204693</v>
       </c>
       <c r="B5" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>122607861</v>
       </c>
       <c r="B4" t="n">
-        <v>97324</v>
+        <v>97326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>123204693</v>
       </c>
       <c r="B5" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>122607861</v>
       </c>
       <c r="B4" t="n">
-        <v>97326</v>
+        <v>97332</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>123204693</v>
       </c>
       <c r="B5" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>122607861</v>
       </c>
       <c r="B4" t="n">
-        <v>97332</v>
+        <v>97335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>123204693</v>
       </c>
       <c r="B5" t="n">
-        <v>97330</v>
+        <v>97333</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>123204693</v>
       </c>
       <c r="B5" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>123204693</v>
       </c>
       <c r="B5" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>123204693</v>
       </c>
       <c r="B5" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>123204693</v>
       </c>
       <c r="B5" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122634371</v>
+        <v>123204664</v>
       </c>
       <c r="B2" t="n">
-        <v>91362</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468912</v>
+        <v>468970</v>
       </c>
       <c r="R2" t="n">
-        <v>6295351</v>
+        <v>6295364</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,17 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på samma träd en äldre och en yngre</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +774,11 @@
           <t>barrskog</t>
         </is>
       </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>grannlaga</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -792,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Darell, Caroline Mortlock</t>
+          <t>Per Darell, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -802,12 +797,7 @@
         <v>122639147</v>
       </c>
       <c r="B3" t="n">
-        <v>94776</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,15 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607861</v>
+        <v>122634371</v>
       </c>
       <c r="B4" t="n">
-        <v>97335</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,45 +920,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224363</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Avd 55, Mellansjön, Sm</t>
+          <t>Mellansjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468898</v>
+        <v>468912</v>
       </c>
       <c r="R4" t="n">
-        <v>6295261</v>
+        <v>6295351</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,12 +985,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på samma träd en äldre och en yngre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,23 +1004,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grova barrträd med torrakor och lågor, fuktig mark intill maden.</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caroline Mortlock</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Caroline Mortlock, Per Darell</t>
+          <t>Per Darell, Caroline Mortlock</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1037,12 +1031,7 @@
         <v>123204693</v>
       </c>
       <c r="B5" t="n">
-        <v>96957</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,6 +1140,116 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122607861</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Avd 55, Mellansjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>468898</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6295261</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Blädinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grova barrträd med torrakor och lågor, fuktig mark intill maden.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123204664</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122639147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122634371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123204693</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,8 +1275,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122607861</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>